--- a/InputData/fuels/BFoICbCTBA/BAU Fraction of Industry Covered by Carbon Tax Border Adjustment.xlsx
+++ b/InputData/fuels/BFoICbCTBA/BAU Fraction of Industry Covered by Carbon Tax Border Adjustment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dobrien\Dropbox (Energy Innovation)\Desktop\Models\U.S. Models\eps-us\InputData\fuels\BFoICbCTBA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\fuels\BFoICbCTBA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F6D53A-89F0-4389-8B9E-98030E37721E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5879F878-C81A-4C46-974B-F2E1F9435F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30495" yWindow="1140" windowWidth="23445" windowHeight="14565" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
+    <workbookView xWindow="8520" yWindow="2835" windowWidth="19200" windowHeight="11205" activeTab="1" xr2:uid="{9AA6BDF2-7B91-4567-88A2-0D83F9E3E450}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <definedName name="N2O_to_CO2e">'[1]Cross-Page Data'!$C$13</definedName>
     <definedName name="unit_conv">[3]About!$A$123</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -771,109 +771,112 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AE28"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.26953125" customWidth="1"/>
-    <col min="2" max="3" width="28" customWidth="1"/>
+    <col min="2" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C1" s="4">
         <v>2021</v>
       </c>
-      <c r="C1" s="4">
+      <c r="D1" s="4">
         <v>2022</v>
       </c>
-      <c r="D1" s="4">
+      <c r="E1" s="4">
         <v>2023</v>
       </c>
-      <c r="E1" s="4">
+      <c r="F1" s="4">
         <v>2024</v>
       </c>
-      <c r="F1" s="4">
+      <c r="G1" s="4">
         <v>2025</v>
       </c>
-      <c r="G1" s="4">
+      <c r="H1" s="4">
         <v>2026</v>
       </c>
-      <c r="H1" s="4">
+      <c r="I1" s="4">
         <v>2027</v>
       </c>
-      <c r="I1" s="4">
+      <c r="J1" s="4">
         <v>2028</v>
       </c>
-      <c r="J1" s="4">
+      <c r="K1" s="4">
         <v>2029</v>
       </c>
-      <c r="K1" s="4">
+      <c r="L1" s="4">
         <v>2030</v>
       </c>
-      <c r="L1" s="4">
+      <c r="M1" s="4">
         <v>2031</v>
       </c>
-      <c r="M1" s="4">
+      <c r="N1" s="4">
         <v>2032</v>
       </c>
-      <c r="N1" s="4">
+      <c r="O1" s="4">
         <v>2033</v>
       </c>
-      <c r="O1" s="4">
+      <c r="P1" s="4">
         <v>2034</v>
       </c>
-      <c r="P1" s="4">
+      <c r="Q1" s="4">
         <v>2035</v>
       </c>
-      <c r="Q1" s="4">
+      <c r="R1" s="4">
         <v>2036</v>
       </c>
-      <c r="R1" s="4">
+      <c r="S1" s="4">
         <v>2037</v>
       </c>
-      <c r="S1" s="4">
+      <c r="T1" s="4">
         <v>2038</v>
       </c>
-      <c r="T1" s="4">
+      <c r="U1" s="4">
         <v>2039</v>
       </c>
-      <c r="U1" s="4">
+      <c r="V1" s="4">
         <v>2040</v>
       </c>
-      <c r="V1" s="4">
+      <c r="W1" s="4">
         <v>2041</v>
       </c>
-      <c r="W1" s="4">
+      <c r="X1" s="4">
         <v>2042</v>
       </c>
-      <c r="X1" s="4">
+      <c r="Y1" s="4">
         <v>2043</v>
       </c>
-      <c r="Y1" s="4">
+      <c r="Z1" s="4">
         <v>2044</v>
       </c>
-      <c r="Z1" s="4">
+      <c r="AA1" s="4">
         <v>2045</v>
       </c>
-      <c r="AA1" s="4">
+      <c r="AB1" s="4">
         <v>2046</v>
       </c>
-      <c r="AB1" s="4">
+      <c r="AC1" s="4">
         <v>2047</v>
       </c>
-      <c r="AC1" s="4">
+      <c r="AD1" s="4">
         <v>2048</v>
       </c>
-      <c r="AD1" s="4">
+      <c r="AE1" s="4">
         <v>2049</v>
       </c>
-      <c r="AE1" s="4">
+      <c r="AF1" s="4">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -881,15 +884,14 @@
         <v>0</v>
       </c>
       <c r="C2" s="5">
-        <f>B2</f>
         <v>0</v>
       </c>
       <c r="D2" s="5">
-        <f t="shared" ref="D2:AE2" si="0">C2</f>
+        <f>C2</f>
         <v>0</v>
       </c>
       <c r="E2" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E2:AF2" si="0">D2</f>
         <v>0</v>
       </c>
       <c r="F2" s="5">
@@ -996,8 +998,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="AF2" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1005,11 +1011,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="5">
-        <f t="shared" ref="C3:AE3" si="1">B3</f>
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D3:AF3" si="1">C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="5">
@@ -1120,8 +1125,12 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
+      <c r="AF3" s="5">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1129,11 +1138,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:AE4" si="2">B4</f>
         <v>1</v>
       </c>
       <c r="D4" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D4:AF4" si="2">C4</f>
         <v>1</v>
       </c>
       <c r="E4" s="5">
@@ -1244,8 +1252,12 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
+      <c r="AF4" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1253,11 +1265,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="5">
-        <f t="shared" ref="C5:AE5" si="3">B5</f>
         <v>1</v>
       </c>
       <c r="D5" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D5:AF5" si="3">C5</f>
         <v>1</v>
       </c>
       <c r="E5" s="5">
@@ -1368,8 +1379,12 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
+      <c r="AF5" s="5">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1377,11 +1392,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="5">
-        <f t="shared" ref="C6:AE6" si="4">B6</f>
         <v>1</v>
       </c>
       <c r="D6" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D6:AF6" si="4">C6</f>
         <v>1</v>
       </c>
       <c r="E6" s="5">
@@ -1492,8 +1506,12 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
+      <c r="AF6" s="5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1501,11 +1519,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="5">
-        <f t="shared" ref="C7:AE7" si="5">B7</f>
         <v>1</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="D7:AF7" si="5">C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="5">
@@ -1616,8 +1633,12 @@
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
+      <c r="AF7" s="5">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1625,11 +1646,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="5">
-        <f t="shared" ref="C8:AE8" si="6">B8</f>
         <v>1</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D8:AF8" si="6">C8</f>
         <v>1</v>
       </c>
       <c r="E8" s="5">
@@ -1740,8 +1760,12 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
+      <c r="AF8" s="5">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1749,11 +1773,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:AE9" si="7">B9</f>
         <v>1</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="D9:AF9" si="7">C9</f>
         <v>1</v>
       </c>
       <c r="E9" s="5">
@@ -1864,8 +1887,12 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
+      <c r="AF9" s="5">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1873,11 +1900,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="5">
-        <f t="shared" ref="C10:AE10" si="8">B10</f>
         <v>1</v>
       </c>
       <c r="D10" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="D10:AF10" si="8">C10</f>
         <v>1</v>
       </c>
       <c r="E10" s="5">
@@ -1988,8 +2014,12 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
+      <c r="AF10" s="5">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1997,11 +2027,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="5">
-        <f t="shared" ref="C11:AE11" si="9">B11</f>
         <v>1</v>
       </c>
       <c r="D11" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D11:AF11" si="9">C11</f>
         <v>1</v>
       </c>
       <c r="E11" s="5">
@@ -2112,8 +2141,12 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
+      <c r="AF11" s="5">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2121,11 +2154,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="5">
-        <f t="shared" ref="C12:AE12" si="10">B12</f>
         <v>1</v>
       </c>
       <c r="D12" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="D12:AF12" si="10">C12</f>
         <v>1</v>
       </c>
       <c r="E12" s="5">
@@ -2236,8 +2268,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
+      <c r="AF12" s="5">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2245,11 +2281,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" ref="C13:AE13" si="11">B13</f>
         <v>1</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="D13:AF13" si="11">C13</f>
         <v>1</v>
       </c>
       <c r="E13" s="5">
@@ -2360,8 +2395,12 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
+      <c r="AF13" s="5">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -2369,11 +2408,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="5">
-        <f t="shared" ref="C14:AE14" si="12">B14</f>
         <v>1</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="D14:AF14" si="12">C14</f>
         <v>1</v>
       </c>
       <c r="E14" s="5">
@@ -2484,8 +2522,12 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
+      <c r="AF14" s="5">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -2493,11 +2535,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="5">
-        <f t="shared" ref="C15:AE15" si="13">B15</f>
         <v>1</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="D15:AF15" si="13">C15</f>
         <v>1</v>
       </c>
       <c r="E15" s="5">
@@ -2608,8 +2649,12 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
+      <c r="AF15" s="5">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -2617,11 +2662,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="5">
-        <f t="shared" ref="C16:AE16" si="14">B16</f>
         <v>1</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="D16:AF16" si="14">C16</f>
         <v>1</v>
       </c>
       <c r="E16" s="5">
@@ -2732,8 +2776,12 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
+      <c r="AF16" s="5">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2741,11 +2789,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17:AE17" si="15">B17</f>
         <v>1</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="D17:AF17" si="15">C17</f>
         <v>1</v>
       </c>
       <c r="E17" s="5">
@@ -2856,8 +2903,12 @@
         <f t="shared" si="15"/>
         <v>1</v>
       </c>
+      <c r="AF17" s="5">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -2865,11 +2916,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18:AE18" si="16">B18</f>
         <v>1</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="D18:AF18" si="16">C18</f>
         <v>1</v>
       </c>
       <c r="E18" s="5">
@@ -2980,8 +3030,12 @@
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
+      <c r="AF18" s="5">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2989,11 +3043,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="5">
-        <f t="shared" ref="C19:AE19" si="17">B19</f>
         <v>1</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="D19:AF19" si="17">C19</f>
         <v>1</v>
       </c>
       <c r="E19" s="5">
@@ -3104,8 +3157,12 @@
         <f t="shared" si="17"/>
         <v>1</v>
       </c>
+      <c r="AF19" s="5">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -3113,11 +3170,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="5">
-        <f t="shared" ref="C20:AE20" si="18">B20</f>
         <v>1</v>
       </c>
       <c r="D20" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="D20:AF20" si="18">C20</f>
         <v>1</v>
       </c>
       <c r="E20" s="5">
@@ -3228,8 +3284,12 @@
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
+      <c r="AF20" s="5">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3237,11 +3297,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="5">
-        <f t="shared" ref="C21:AE21" si="19">B21</f>
         <v>1</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="D21:AF21" si="19">C21</f>
         <v>1</v>
       </c>
       <c r="E21" s="5">
@@ -3352,8 +3411,12 @@
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
+      <c r="AF21" s="5">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -3361,11 +3424,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="5">
-        <f t="shared" ref="C22:AE22" si="20">B22</f>
         <v>1</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="D22:AF22" si="20">C22</f>
         <v>1</v>
       </c>
       <c r="E22" s="5">
@@ -3476,8 +3538,12 @@
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
+      <c r="AF22" s="5">
+        <f t="shared" si="20"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -3485,11 +3551,10 @@
         <v>1</v>
       </c>
       <c r="C23" s="5">
-        <f t="shared" ref="C23:AE23" si="21">B23</f>
         <v>1</v>
       </c>
       <c r="D23" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="D23:AF23" si="21">C23</f>
         <v>1</v>
       </c>
       <c r="E23" s="5">
@@ -3600,8 +3665,12 @@
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
+      <c r="AF23" s="5">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -3609,11 +3678,10 @@
         <v>1</v>
       </c>
       <c r="C24" s="5">
-        <f t="shared" ref="C24:AE24" si="22">B24</f>
         <v>1</v>
       </c>
       <c r="D24" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="D24:AF24" si="22">C24</f>
         <v>1</v>
       </c>
       <c r="E24" s="5">
@@ -3724,8 +3792,12 @@
         <f t="shared" si="22"/>
         <v>1</v>
       </c>
+      <c r="AF24" s="5">
+        <f t="shared" si="22"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -3733,11 +3805,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="5">
-        <f t="shared" ref="C25:AE25" si="23">B25</f>
         <v>0</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="D25:AF25" si="23">C25</f>
         <v>0</v>
       </c>
       <c r="E25" s="5">
@@ -3848,8 +3919,12 @@
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
+      <c r="AF25" s="5">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -3857,11 +3932,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="5">
-        <f t="shared" ref="C26:AE26" si="24">B26</f>
         <v>1</v>
       </c>
       <c r="D26" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="D26:AF26" si="24">C26</f>
         <v>1</v>
       </c>
       <c r="E26" s="5">
@@ -3972,10 +4046,15 @@
         <f t="shared" si="24"/>
         <v>1</v>
       </c>
+      <c r="AF26" s="5">
+        <f t="shared" si="24"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4127,6 +4206,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4135,20 +4220,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5EE18B8-7955-4D84-849A-DF6B586BB12F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5EE18B8-7955-4D84-849A-DF6B586BB12F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7EA50C-F93D-4BCE-98C1-03A6BC9A7F4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{079D8A0A-6A76-482E-A15E-4FE413986454}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{079D8A0A-6A76-482E-A15E-4FE413986454}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB7EA50C-F93D-4BCE-98C1-03A6BC9A7F4C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>